--- a/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs. Papa dit : voici l'espace du jeu. Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Papa dit : on va passer le ballon. Chacun a son tour. Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
+          <t>Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs. Voici l'espace du jeu. Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. On va passer le ballon. Chacun a son tour. Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs.
+papa|Voici l'espace du jeu.
+narrateur|Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd.
+papa|On va passer le ballon. Chacun a son tour.
+narrateur|Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ugo a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ugo a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Ugo boit de l'eau. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Ugo a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Ugo a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Papa range le ballon. Ugo boit de l'eau. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ugo passe le ballon</t>
+          <t>Nino passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Nino et papa se passent le ballon dans l'espace du jeu. Nino attend son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs. Voici l'espace du jeu. Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. On va passer le ballon. Chacun a son tour. Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe dans la barquette. Ça fait un petit cercle. L'herbe brille comme de l'eau. La terre sent le jardin mouillé. Deux bottes jaunes sèchent près de la porte. Un oiseau secoue ses ailes. Nino, viens voir le jardin. En ce moment, Nino pose un pied dehors. L'herbe est froide et douce. Une petite flaque brille près du bac. Ça brille, papa. Oui. C'est après la pluie. Papa pose deux sacs verts. Les sacs font un petit bruit. Voici l'espace du jeu. Nino reste dans l'espace du jeu. Le ballon est près d'un sac. Il est jaune et un peu lourd. Il sent l'herbe mouillée. Il est lourd, papa. Oui. On va passer le ballon. Chacun a son tour. Papa donne le ballon. Nino le tient avec les deux mains. C'est ton tour, Nino. Nino passe le ballon à papa. Le ballon fait un petit bruit mou. Papa l'attrape. Bravo. J'ai le ballon. Maintenant, c'est mon tour. Nino attend. Ses pieds restent dans l'espace. Une goutte tombe encore. Papa passe le ballon. Nino l'attrape contre son ventre. C'est mon tour ? Oui. C'est ton tour. Nino passe encore. Papa l'attrape près du sac. Bien joué. Tu as attendu. Un oiseau chante sur la gouttière. Nino reste dans l'espace du jeu. On reste dans l'espace du jeu. Nino attend encore. Il regarde le ballon jaune. Puis c'est son tour. Il passe le ballon. Tu passes. Tu attends. Bravo. Le ballon est un peu mouillé. Nino le sent. Il est doux. Encore, papa. Oui. Encore un tour. Papa passe le ballon tout doucement. Nino attend, puis il passe. Tu restes dans l'espace. Bravo. La gouttière fait encore plic. Une petite menthe sent fort près du mur. Tu aimes cette odeur ? Oui. Ça sent bon. Le ballon revient dans ses mains. C'est ton tour. Tu passes. Nino passe le ballon. Merci. J'attends, puis je passe. Nino reste dans l'espace du jeu. Ses chaussettes sont un peu mouillées. Mes pieds sont froids. On rentrera après. Encore un passage. Nino attend son tour. Papa passe. Nino attrape. Nino passe. Merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,80 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs.
+          <t>narrateur|La gouttière fait plic, plic, plic.
+narrateur|Une goutte tombe dans la barquette.
+narrateur|Ça fait un petit cercle.
+narrateur|L'herbe brille comme de l'eau.
+narrateur|La terre sent le jardin mouillé.
+narrateur|Deux bottes jaunes sèchent près de la porte.
+narrateur|Un oiseau secoue ses ailes.
+papa|Nino, viens voir le jardin.
+narrateur|En ce moment, Nino pose un pied dehors.
+narrateur|L'herbe est froide et douce.
+narrateur|Une petite flaque brille près du bac.
+enfant-m|Ça brille, papa.
+papa|Oui. C'est après la pluie.
+narrateur|Papa pose deux sacs verts.
+narrateur|Les sacs font un petit bruit.
 papa|Voici l'espace du jeu.
-narrateur|Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd.
-papa|On va passer le ballon. Chacun a son tour.
-narrateur|Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nino reste dans l'espace du jeu.
+narrateur|Le ballon est près d'un sac.
+narrateur|Il est jaune et un peu lourd.
+narrateur|Il sent l'herbe mouillée.
+enfant-m|Il est lourd, papa.
+papa|Oui. On va passer le ballon.
+papa|Chacun a son tour.
+narrateur|Papa donne le ballon.
+narrateur|Nino le tient avec les deux mains.
+papa|C'est ton tour, Nino.
+narrateur|Nino passe le ballon à papa.
+narrateur|Le ballon fait un petit bruit mou.
+narrateur|Papa l'attrape.
+papa|Bravo. J'ai le ballon.
+papa|Maintenant, c'est mon tour.
+narrateur|Nino attend.
+narrateur|Ses pieds restent dans l'espace.
+narrateur|Une goutte tombe encore.
+narrateur|Papa passe le ballon.
+narrateur|Nino l'attrape contre son ventre.
+enfant-m|C'est mon tour ?
+papa|Oui. C'est ton tour.
+narrateur|Nino passe encore.
+narrateur|Papa l'attrape près du sac.
+papa|Bien joué. Tu as attendu.
+narrateur|Un oiseau chante sur la gouttière.
+narrateur|Nino reste dans l'espace du jeu.
+papa|On reste dans l'espace du jeu.
+narrateur|Nino attend encore.
+narrateur|Il regarde le ballon jaune.
+narrateur|Puis c'est son tour.
+narrateur|Il passe le ballon.
+papa|Tu passes. Tu attends. Bravo.
+narrateur|Le ballon est un peu mouillé.
+narrateur|Nino le sent. Il est doux.
+enfant-m|Encore, papa.
+papa|Oui. Encore un tour.
+narrateur|Papa passe le ballon tout doucement.
+narrateur|Nino attend, puis il passe.
+papa|Tu restes dans l'espace. Bravo.
+narrateur|La gouttière fait encore plic.
+narrateur|Une petite menthe sent fort près du mur.
+papa|Tu aimes cette odeur ?
+enfant-m|Oui. Ça sent bon.
+narrateur|Le ballon revient dans ses mains.
+papa|C'est ton tour. Tu passes.
+narrateur|Nino passe le ballon.
+papa|Merci. J'attends, puis je passe.
+narrateur|Nino reste dans l'espace du jeu.
+narrateur|Ses chaussettes sont un peu mouillées.
+enfant-m|Mes pieds sont froids.
+papa|On rentrera après. Encore un passage.
+narrateur|Nino attend son tour.
+narrateur|Papa passe. Nino attrape.
+narrateur|Nino passe.
+papa|Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1422,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ugo a le ballon. Que fait-il ?</t>
+          <t>Nino a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1578,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ugo a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ugo a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+          <t>Nino a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a son tour. Oui. Bravo, Nino. L'herbe brille encore. La gouttière fait un dernier plic.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1750,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ugo a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a passé le ballon.
+narrateur|Il a attendu son tour.
+narrateur|Il est resté dans l'espace du jeu.
+papa|Tu as passé. Tu as attendu.
+papa|Tu es resté dans l'espace.
+enfant-m|Chacun a son tour.
+papa|Oui. Bravo, Nino.
+narrateur|L'herbe brille encore.
+narrateur|La gouttière fait un dernier plic.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Ugo boit de l'eau. Ils rentrent.</t>
+          <t>Papa range le ballon dans un sac. Le sac est un peu mouillé. Tu veux de l'eau ? Oui, papa. Nino boit une gorgée. L'eau est fraîche. On rentre. Les bottes attendent. Nino enfile une botte jaune. Ils rentrent. La gouttière fait encore plic.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,10 +1921,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Ugo boit de l'eau. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon dans un sac.
+narrateur|Le sac est un peu mouillé.
+papa|Tu veux de l'eau ?
+enfant-m|Oui, papa.
+narrateur|Nino boit une gorgée.
+narrateur|L'eau est fraîche.
+papa|On rentre. Les bottes attendent.
+narrateur|Nino enfile une botte jaune.
+narrateur|Ils rentrent.
+narrateur|La gouttière fait encore plic.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon est dans le sac. Nino a passé. Il a attendu. Bravo, Nino. Tu as bien joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,10 +2097,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon est dans le sac.
+narrateur|Nino a passé. Il a attendu.
+papa|Bravo, Nino. Tu as bien joué.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ugo et papa sont au jardin. L'herbe est douce. Papa pose deux sacs. Papa dit : voici l'espace du jeu. Ugo reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Papa dit : on va &lt;emphasis level="moderate"&gt;passer&lt;/emphasis&gt; le ballon. Chacun a son tour. Ugo passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Ugo attend. Puis c'est son tour. Ugo passe encore. Ugo reste dans l'espace. Il attend. Il passe.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe dans la barquette. Ça fait un petit cercle. L'herbe brille comme de l'eau. La terre sent le jardin mouillé. Deux bottes jaunes sèchent près de la porte. Un oiseau secoue ses ailes. Nino, viens voir le jardin. En ce moment, Nino pose un pied dehors. L'herbe est froide et douce. Une petite flaque brille près du bac. Ça brille, papa. Oui. C'est après la pluie. Papa pose deux sacs verts. Les sacs font un petit bruit. Voici l'espace du jeu. Nino reste dans l'espace du jeu. Le ballon est près d'un sac. Il est jaune et un peu lourd. Il sent l'herbe mouillée. Il est lourd, papa. Oui. On va passer le ballon. Chacun a son tour. Papa donne le ballon. Nino le tient avec les deux mains. C'est ton tour, Nino. Nino passe le ballon à papa. Le ballon fait un petit bruit mou. Papa l'attrape. Bravo. J'ai le ballon. Maintenant, c'est mon tour. Nino attend. Ses pieds restent dans l'espace. Une goutte tombe encore. Papa passe le ballon. Nino l'attrape contre son ventre. C'est mon tour ? Oui. C'est ton tour. Nino passe encore. Papa l'attrape près du sac. Bien joué. Tu as attendu. Un oiseau chante sur la gouttière. Nino reste dans l'espace du jeu. On reste dans l'espace du jeu. Nino attend encore. Il regarde le ballon jaune. Puis c'est son tour. Il passe le ballon. Tu passes. Tu attends. Bravo. Le ballon est un peu mouillé. Nino le sent. Il est doux. Encore, papa. Oui. Encore un tour. Papa passe le ballon tout doucement. Nino attend, puis il passe. Tu restes dans l'espace. Bravo. La gouttière fait encore plic. Une petite menthe sent fort près du mur. Tu aimes cette odeur ? Oui. Ça sent bon. Le ballon revient dans ses mains. C'est ton tour. Tu passes. Nino passe le ballon. Merci. J'attends, puis je passe. Nino reste dans l'espace du jeu. Ses chaussettes sont un peu mouillées. Mes pieds sont froids. On rentrera après. Encore un passage. Nino attend son tour. Papa passe. Nino attrape. Nino passe. Merci.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ugo a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ugo a passé le ballon. Il a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Il est resté dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a son tour. Oui. Bravo, Nino. L'herbe brille encore. La gouttière fait un dernier plic.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa range le ballon. Ugo boit de l'eau. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon dans un sac. Le sac est un peu mouillé. Tu veux de l'eau ? Oui, papa. Nino boit une gorgée. L'eau est fraîche. On rentre. Les bottes attendent. Nino enfile une botte jaune. Ils rentrent. La gouttière fait encore plic.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon est dans le sac. Nino a passé. Il a attendu. Bravo, Nino. Tu as bien joué. L'histoire est finie.</t>
+          <t>Le ballon est dans le sac. Nino a passé. Il a attendu. Bravo, Nino. Tu as bien joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon est dans le sac. Nino a passé. Il a attendu. Bravo, Nino. Tu as bien joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,8 +2099,7 @@
         <is>
           <t>narrateur|Le ballon est dans le sac.
 narrateur|Nino a passé. Il a attendu.
-papa|Bravo, Nino. Tu as bien joué.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Nino. Tu as bien joué.</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ugo, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
